--- a/data/trans_orig/IP07_C11_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C11_2023-Estudios-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tener problemas para dormir en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de tener problemas para dormir, percibida por el/la menor en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1640</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2279</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6088</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,22%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7806</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>16,33%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>49,07%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>55,96%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2279</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>9913</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>7,42%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1640</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6239</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>5,62%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>897</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>801</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,22 +1021,22 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>832</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>7789</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4150</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1127</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7954</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>24,76%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,73%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>47,45%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1865</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4724</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>15,03%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>38,08%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>393</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7985</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5759</t>
+          <t>6142</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>2590</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>10904</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>35,5%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9903</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6306</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13959</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>59,07%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>37,62%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>83,27%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7066</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3658</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9750</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>56,95%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>29,48%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>78,58%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10309</t>
+          <t>7720</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13749</t>
+          <t>11248</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>17376</t>
+          <t>17623</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12533</t>
+          <t>11889</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21892</t>
+          <t>22421</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>73,0%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6953</t>
+          <t>9430</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9793</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6767</t>
+          <t>7512</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>14870</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3060</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8066</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>4129</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1388</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8751</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>1586</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7942</t>
+          <t>8873</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>7324</t>
+          <t>7515</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13917</t>
+          <t>13254</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2689</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2564</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>6578</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,13%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>764</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>30001</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20712</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>44389</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,98%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,34%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>46009</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>20592</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>90241</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>28,88%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,93%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>56,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29336</t>
+          <t>22818</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19434</t>
+          <t>15606</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43440</t>
+          <t>32707</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>75345</t>
+          <t>52819</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47518</t>
+          <t>41687</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143334</t>
+          <t>71347</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>162777</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>148829</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>173589</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>81,25%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>74,29%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>86,65%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>103678</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>62213</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>127530</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>65,08%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>39,05%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>80,05%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>165735</t>
+          <t>109185</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>150604</t>
+          <t>99212</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>176435</t>
+          <t>118555</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>269413</t>
+          <t>271962</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>204053</t>
+          <t>254667</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>297077</t>
+          <t>285473</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>83,23%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>362013</t>
+          <t>343002</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>362013</t>
+          <t>343002</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>362013</t>
+          <t>343002</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>586</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>862</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3126</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8051</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>15,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>806</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>4463</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>4472</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>11,52%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3143</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>9610</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10132</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>891</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8753</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>10064</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5648</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>15020</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>18,99%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>10,66%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>28,34%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>4231</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1704</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>8222</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>10,92%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>21,22%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16611</t>
+          <t>8906</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>14593</t>
+          <t>14753</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9817</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21673</t>
+          <t>21189</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>37717</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>31398</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>43255</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>71,16%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>59,24%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>81,61%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>31002</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>26152</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>34818</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>80,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>67,49%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>89,85%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>37141</t>
+          <t>32565</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30384</t>
+          <t>27126</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42474</t>
+          <t>36457</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>68143</t>
+          <t>70282</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>60240</t>
+          <t>62157</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>74381</t>
+          <t>77145</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>82,09%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4510</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>9456</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>5394</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2112</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>11524</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>14377</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17603</t>
+          <t>20825</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10518</t>
+          <t>13926</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14624</t>
+          <t>11569</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>13184</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>7319</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21086</t>
+          <t>21076</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>3897</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>8931</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>5576</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>2519</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>12080</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>2417</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8395</t>
+          <t>11506</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,22 +3067,22 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>9369</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15826</t>
+          <t>16722</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>44215</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>33013</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>60148</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>16,37%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>12,22%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>22,27%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>52104</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>26081</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>109831</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>24,76%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>12,39%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>52,18%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>43592</t>
+          <t>29499</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31683</t>
+          <t>21119</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>57711</t>
+          <t>41169</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>95697</t>
+          <t>73714</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>68156</t>
+          <t>58318</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>165121</t>
+          <t>92530</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>210396</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>193599</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>223193</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>77,9%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>71,68%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>82,63%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>141745</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>92958</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>167316</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>67,35%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>44,17%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>79,5%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>213186</t>
+          <t>149470</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>197874</t>
+          <t>138189</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>226249</t>
+          <t>160236</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>354931</t>
+          <t>359867</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>292251</t>
+          <t>338542</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>382548</t>
+          <t>377405</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>80,7%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
